--- a/RMTest-5.xlsx
+++ b/RMTest-5.xlsx
@@ -124,18 +124,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF86A5A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -150,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -166,9 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,19 +504,19 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>5.033</v>
+        <v>4.957</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>4.964</v>
+        <v>5.007</v>
       </c>
       <c r="H2" s="4">
-        <v>0.006892</v>
+        <v>-0.004954</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -539,10 +530,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>5.033</v>
+        <v>4.961</v>
       </c>
       <c r="E3" s="1">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -559,19 +550,19 @@
         <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>6.274</v>
+        <v>6.178</v>
       </c>
       <c r="E4" s="1">
         <v>49.8</v>
       </c>
       <c r="F4" s="1">
-        <v>25.5</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3">
-        <v>6.256</v>
+        <v>6.216</v>
       </c>
       <c r="H4" s="4">
-        <v>0.001819</v>
+        <v>-0.003811</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -585,19 +576,19 @@
         <v>7.5</v>
       </c>
       <c r="D5" s="3">
-        <v>7.514</v>
+        <v>7.455</v>
       </c>
       <c r="E5" s="1">
         <v>74.8</v>
       </c>
       <c r="F5" s="1">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3">
-        <v>7.524</v>
+        <v>7.475</v>
       </c>
       <c r="H5" s="4">
-        <v>-0.001072</v>
+        <v>-0.00193</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -611,19 +602,19 @@
         <v>8.75</v>
       </c>
       <c r="D6" s="3">
-        <v>8.778</v>
+        <v>8.731</v>
       </c>
       <c r="E6" s="1">
         <v>99.8</v>
       </c>
       <c r="F6" s="1">
-        <v>75.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G6" s="3">
-        <v>8.789</v>
+        <v>8.733000000000001</v>
       </c>
       <c r="H6" s="4">
-        <v>-0.001089</v>
+        <v>-0.000225</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -637,19 +628,19 @@
         <v>10</v>
       </c>
       <c r="D7" s="3">
-        <v>9.997</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="E7" s="1">
-        <v>123.7</v>
+        <v>124.9</v>
       </c>
       <c r="F7" s="1">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>-0.000276</v>
+        <v>-9.8E-05</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -657,7 +648,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="C8" s="2">
         <v>10</v>
@@ -666,10 +657,10 @@
         <v>9.999000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="F8" s="1">
-        <v>141.1</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -683,10 +674,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>5.022</v>
+        <v>4.957</v>
       </c>
       <c r="E9" s="1">
-        <v>-25.8</v>
+        <v>-24.6</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -703,19 +694,19 @@
         <v>3.75</v>
       </c>
       <c r="D10" s="3">
-        <v>3.788</v>
+        <v>3.69</v>
       </c>
       <c r="E10" s="1">
-        <v>-50.3</v>
+        <v>-50.1</v>
       </c>
       <c r="F10" s="1">
-        <v>-24.5</v>
+        <v>-25.5</v>
       </c>
       <c r="G10" s="3">
         <v>3.722</v>
       </c>
       <c r="H10" s="4">
-        <v>0.006603</v>
+        <v>-0.003187</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -729,19 +720,19 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="3">
-        <v>2.512</v>
+        <v>2.435</v>
       </c>
       <c r="E11" s="1">
         <v>-75.09999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>-49.3</v>
+        <v>-50.5</v>
       </c>
       <c r="G11" s="3">
-        <v>2.467</v>
+        <v>2.459</v>
       </c>
       <c r="H11" s="4">
-        <v>0.004543</v>
+        <v>-0.002441</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -755,19 +746,19 @@
         <v>1.25</v>
       </c>
       <c r="D12" s="3">
-        <v>1.219</v>
+        <v>1.188</v>
       </c>
       <c r="E12" s="1">
-        <v>-100.2</v>
+        <v>-100.1</v>
       </c>
       <c r="F12" s="1">
-        <v>-74.40000000000001</v>
+        <v>-75.5</v>
       </c>
       <c r="G12" s="3">
-        <v>1.193</v>
+        <v>1.201</v>
       </c>
       <c r="H12" s="4">
-        <v>0.002537</v>
+        <v>-0.001221</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -781,19 +772,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>-123.8</v>
+        <v>-123.9</v>
       </c>
       <c r="F13" s="1">
-        <v>-98</v>
+        <v>-99.3</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.000192</v>
+        <v>1.5E-05</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -801,7 +792,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -810,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="F14" s="1">
-        <v>-139.6</v>
+        <v>-140.9</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -821,13 +812,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="6">
-        <v>0.006892</v>
+      <c r="H16" s="4">
+        <v>1.5E-05</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -835,13 +826,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="6">
-        <v>-0.001089</v>
+      <c r="H17" s="4">
+        <v>-0.004954</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -849,7 +840,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>98</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -857,7 +848,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="1">
-        <v>197.4</v>
+        <v>198.4</v>
       </c>
     </row>
   </sheetData>
